--- a/Downloads/order-invoice_ahmedrashaad3.xlsx
+++ b/Downloads/order-invoice_ahmedrashaad3.xlsx
@@ -421,7 +421,7 @@
     </row>
     <row r="2">
       <c r="A2" t="str">
-        <v>66e5e813ae2afd4c0b74d1e2</v>
+        <v>66e6ea08ae2afd4c0b758748</v>
       </c>
       <c r="B2" t="str">
         <v>IPHONE 13 PRO</v>
